--- a/output/二等水准观测手簿.xlsx
+++ b/output/二等水准观测手簿.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B (H=50.200m)</t>
+          <t>B (H=2.664m)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G (H=52.800m)</t>
+          <t>G (H=9.971m)</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="24" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
   </cols>
@@ -737,43 +737,43 @@
         <v>4.9678</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3244</v>
+        <v>3.0735</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8802</v>
+        <v>2.6293</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1023</v>
+        <v>2.8514</v>
       </c>
       <c r="K2" t="n">
-        <v>5.1178</v>
+        <v>5.8669</v>
       </c>
       <c r="L2" t="n">
         <v>44.90000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>44.41999999999997</v>
+        <v>44.41999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4800000000000324</v>
+        <v>0.4800000000000111</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4800000000000324</v>
+        <v>0.4800000000000111</v>
       </c>
       <c r="P2" t="n">
         <v>-8.881784197001252e-13</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-13</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1500000000000001</v>
+        <v>-0.8991</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1499999999999995</v>
+        <v>-0.8990999999999998</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1499999999999998</v>
+        <v>-0.8990999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -787,7 +787,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>TP.1.2</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -803,16 +803,16 @@
         <v>4.9216</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2162</v>
+        <v>2.9653</v>
       </c>
       <c r="I3" t="n">
-        <v>1.896</v>
+        <v>2.6451</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0561</v>
+        <v>2.8052</v>
       </c>
       <c r="K3" t="n">
-        <v>5.0716</v>
+        <v>5.8207</v>
       </c>
       <c r="L3" t="n">
         <v>32.05999999999997</v>
@@ -824,7 +824,7 @@
         <v>0.03999999999994941</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5199999999999818</v>
+        <v>0.5199999999999605</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -833,13 +833,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1499999999999999</v>
+        <v>-0.8991000000000002</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1500000000000004</v>
+        <v>-0.8991000000000007</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1500000000000001</v>
+        <v>-0.8991000000000005</v>
       </c>
     </row>
     <row r="4">
@@ -848,12 +848,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>TP.1.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TP.2.1</t>
+          <t>K12</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -869,43 +869,43 @@
         <v>5.2088</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4655</v>
+        <v>3.2146</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2211</v>
+        <v>2.9702</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3433</v>
+        <v>3.0924</v>
       </c>
       <c r="K4" t="n">
-        <v>5.3588</v>
+        <v>6.1079</v>
       </c>
       <c r="L4" t="n">
         <v>25.04</v>
       </c>
       <c r="M4" t="n">
-        <v>24.44000000000002</v>
+        <v>24.43999999999997</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5999999999999766</v>
+        <v>0.6000000000000227</v>
       </c>
       <c r="O4" t="n">
-        <v>1.119999999999958</v>
+        <v>1.119999999999983</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.881784197001252e-13</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1500000000000004</v>
+        <v>-0.8991000000000002</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1499999999999995</v>
+        <v>-0.8990999999999998</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1499999999999999</v>
+        <v>-0.8991</v>
       </c>
     </row>
     <row r="5">
@@ -914,37 +914,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TP.2.1</t>
+          <t>K12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K11</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.3808</v>
+        <v>2.5591</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1328</v>
+        <v>2.3111</v>
       </c>
       <c r="F5" t="n">
+        <v>2.4351</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.4506</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.3772</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.1364</v>
+      </c>
+      <c r="J5" t="n">
         <v>2.2568</v>
       </c>
-      <c r="G5" t="n">
+      <c r="K5" t="n">
         <v>5.2723</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.5272</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.2864</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.4068</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.4223</v>
       </c>
       <c r="L5" t="n">
         <v>24.79999999999998</v>
@@ -956,22 +956,22 @@
         <v>0.7199999999999633</v>
       </c>
       <c r="O5" t="n">
-        <v>1.839999999999922</v>
+        <v>1.839999999999947</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-8.881784197001252e-13</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
-        <v>-0.1499999999999999</v>
+        <v>0.1782999999999997</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1499999999999995</v>
+        <v>0.1782999999999992</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1499999999999997</v>
+        <v>0.1782999999999995</v>
       </c>
     </row>
     <row r="6">
@@ -980,49 +980,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TP.3.1</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.6024</v>
+        <v>3.0556</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1228</v>
+        <v>2.576</v>
       </c>
       <c r="F6" t="n">
+        <v>2.8158</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.8313</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.6037</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.1215</v>
+      </c>
+      <c r="J6" t="n">
         <v>2.3626</v>
       </c>
-      <c r="G6" t="n">
+      <c r="K6" t="n">
         <v>5.3781</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.7704</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.2882</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.5293</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.5448</v>
       </c>
       <c r="L6" t="n">
         <v>47.96</v>
       </c>
       <c r="M6" t="n">
-        <v>48.22000000000002</v>
+        <v>48.21999999999997</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2600000000000193</v>
+        <v>-0.2599999999999696</v>
       </c>
       <c r="O6" t="n">
-        <v>1.579999999999902</v>
+        <v>1.579999999999977</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1031,13 +1031,13 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1667000000000001</v>
+        <v>0.4531999999999998</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1667000000000005</v>
+        <v>0.4531999999999998</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1667000000000003</v>
+        <v>0.4531999999999998</v>
       </c>
     </row>
     <row r="7">
@@ -1046,64 +1046,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TP.3.1</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TP.3.2</t>
+          <t>TP.4.1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.6945</v>
+        <v>2.3269</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3653</v>
+        <v>1.9977</v>
       </c>
       <c r="F7" t="n">
+        <v>2.1623</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.1778</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.6967</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.3631</v>
+      </c>
+      <c r="J7" t="n">
         <v>1.5299</v>
       </c>
-      <c r="G7" t="n">
+      <c r="K7" t="n">
         <v>4.5454</v>
       </c>
-      <c r="H7" t="n">
-        <v>1.8634</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.5298</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.6966</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.7121</v>
-      </c>
       <c r="L7" t="n">
-        <v>32.91999999999999</v>
+        <v>32.92000000000002</v>
       </c>
       <c r="M7" t="n">
-        <v>33.35999999999999</v>
+        <v>33.36000000000001</v>
       </c>
       <c r="N7" t="n">
         <v>-0.4399999999999977</v>
       </c>
       <c r="O7" t="n">
-        <v>1.139999999999905</v>
+        <v>1.139999999999979</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-13</v>
       </c>
       <c r="Q7" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1667000000000001</v>
+        <v>0.6324000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1667000000000005</v>
+        <v>0.6324000000000005</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1667000000000003</v>
+        <v>0.6324000000000003</v>
       </c>
     </row>
     <row r="8">
@@ -1112,49 +1112,49 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TP.3.2</t>
+          <t>TP.4.1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K9</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.9769</v>
+        <v>2.6092</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5469</v>
+        <v>2.1792</v>
       </c>
       <c r="F8" t="n">
+        <v>2.3942</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.4097</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.9787</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.5451</v>
+      </c>
+      <c r="J8" t="n">
         <v>1.7619</v>
       </c>
-      <c r="G8" t="n">
+      <c r="K8" t="n">
         <v>4.7774</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.1453</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.7117</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.9285</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.944</v>
       </c>
       <c r="L8" t="n">
         <v>43.00000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>43.36000000000002</v>
+        <v>43.36</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3600000000000065</v>
+        <v>-0.3599999999999852</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7799999999998981</v>
+        <v>0.779999999999994</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1163,13 +1163,13 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.1666000000000001</v>
+        <v>0.6323000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1665999999999999</v>
+        <v>0.6322999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1666</v>
+        <v>0.6323</v>
       </c>
     </row>
     <row r="9">
@@ -1178,64 +1178,64 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>TP.5.1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.3335</v>
+        <v>2.1335</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9527</v>
+        <v>1.7527</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1431</v>
+        <v>1.9431</v>
       </c>
       <c r="G9" t="n">
-        <v>5.1586</v>
+        <v>4.9586</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1356</v>
+        <v>2.9212</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7506</v>
+        <v>2.5362</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9431</v>
+        <v>2.7287</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9586</v>
+        <v>5.7442</v>
       </c>
       <c r="L9" t="n">
-        <v>38.07999999999998</v>
+        <v>38.08000000000003</v>
       </c>
       <c r="M9" t="n">
-        <v>38.50000000000002</v>
+        <v>38.49999999999998</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4200000000000372</v>
+        <v>-0.419999999999952</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3599999999998609</v>
+        <v>0.3600000000000421</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-13</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2</v>
+        <v>-0.7855999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2000000000000002</v>
+        <v>-0.7856000000000005</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2000000000000001</v>
+        <v>-0.7856000000000002</v>
       </c>
     </row>
     <row r="10">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>TP.5.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TP.5.1</t>
+          <t>TP.5.2</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1265,16 +1265,16 @@
         <v>5.0217</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3648</v>
+        <v>3.017</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9144</v>
+        <v>2.5666</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1396</v>
+        <v>2.7918</v>
       </c>
       <c r="K10" t="n">
-        <v>5.1551</v>
+        <v>5.8073</v>
       </c>
       <c r="L10" t="n">
         <v>44.57999999999998</v>
@@ -1286,7 +1286,7 @@
         <v>-0.4599999999999937</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1000000000001329</v>
+        <v>-0.09999999999995168</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.1334</v>
+        <v>-0.7855999999999996</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1334</v>
+        <v>-0.7855999999999996</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1334</v>
+        <v>-0.7855999999999996</v>
       </c>
     </row>
     <row r="11">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TP.5.1</t>
+          <t>TP.5.2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TP.5.2</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1331,43 +1331,43 @@
         <v>5.1439</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3632</v>
+        <v>3.0154</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1602</v>
+        <v>2.8124</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2617</v>
+        <v>2.9139</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2772</v>
+        <v>5.9294</v>
       </c>
       <c r="L11" t="n">
         <v>20.72000000000003</v>
       </c>
       <c r="M11" t="n">
-        <v>20.29999999999998</v>
+        <v>20.30000000000003</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4200000000000443</v>
+        <v>0.4199999999999982</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3199999999999115</v>
+        <v>0.3200000000000465</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-13</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.1332999999999998</v>
+        <v>-0.7854999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1332999999999993</v>
+        <v>-0.7854999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1332999999999995</v>
+        <v>-0.7854999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TP.5.2</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>TP.6.1</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1397,43 +1397,43 @@
         <v>4.7349</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0838</v>
+        <v>2.7952</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6216</v>
+        <v>2.333</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8527</v>
+        <v>2.5641</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8682</v>
+        <v>5.5796</v>
       </c>
       <c r="L12" t="n">
         <v>46.23999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>46.22000000000001</v>
+        <v>46.21999999999997</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01999999999998181</v>
+        <v>0.02000000000002444</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3399999999998933</v>
+        <v>0.3400000000000709</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-13</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.1333</v>
+        <v>-0.8446999999999998</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1333000000000002</v>
+        <v>-0.8447000000000005</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1333000000000001</v>
+        <v>-0.8447000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>TP.6.1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TP.6.1</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1463,16 +1463,16 @@
         <v>5.0139</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3035</v>
+        <v>2.9983</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9933</v>
+        <v>2.6881</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1484</v>
+        <v>2.8432</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1639</v>
+        <v>5.8587</v>
       </c>
       <c r="L13" t="n">
         <v>30.58000000000001</v>
@@ -1484,7 +1484,7 @@
         <v>-0.4399999999999977</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1000000000001044</v>
+        <v>-0.09999999999992681</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1493,13 +1493,13 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.1500000000000001</v>
+        <v>-0.8448</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1500000000000004</v>
+        <v>-0.8448000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1500000000000002</v>
+        <v>-0.8448000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TP.6.1</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>TP.7.1</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1529,16 +1529,16 @@
         <v>5.4705</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7844</v>
+        <v>3.3161</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4256</v>
+        <v>2.9573</v>
       </c>
       <c r="J14" t="n">
-        <v>2.605</v>
+        <v>3.1367</v>
       </c>
       <c r="K14" t="n">
-        <v>5.6205</v>
+        <v>6.1522</v>
       </c>
       <c r="L14" t="n">
         <v>35.28000000000002</v>
@@ -1550,7 +1550,7 @@
         <v>-0.5999999999999801</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7000000000000846</v>
+        <v>-0.6999999999999069</v>
       </c>
       <c r="P14" t="n">
         <v>-8.881784197001252e-13</v>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1499999999999999</v>
+        <v>-0.6816999999999998</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1499999999999995</v>
+        <v>-0.6816999999999993</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1499999999999997</v>
+        <v>-0.6816999999999995</v>
       </c>
     </row>
     <row r="15">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>TP.7.1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TP.7.1</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1595,28 +1595,28 @@
         <v>4.9936</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3159</v>
+        <v>2.8642</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9069</v>
+        <v>2.4552</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1114</v>
+        <v>2.6597</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1269</v>
+        <v>5.6752</v>
       </c>
       <c r="L15" t="n">
         <v>40.38000000000002</v>
       </c>
       <c r="M15" t="n">
-        <v>40.90000000000001</v>
+        <v>40.89999999999998</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5199999999999889</v>
+        <v>-0.5199999999999605</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.220000000000073</v>
+        <v>-1.219999999999867</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1625,13 +1625,13 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.1333000000000002</v>
+        <v>-0.6816</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1333000000000002</v>
+        <v>-0.6816000000000004</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1333000000000002</v>
+        <v>-0.6816000000000002</v>
       </c>
     </row>
     <row r="16">
@@ -1640,37 +1640,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TP.7.1</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TP.7.2</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2.182</v>
+        <v>3.3041</v>
       </c>
       <c r="E16" t="n">
-        <v>1.749</v>
+        <v>2.8711</v>
       </c>
       <c r="F16" t="n">
+        <v>3.0876</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6.1031</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.1811</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.7499</v>
+      </c>
+      <c r="J16" t="n">
         <v>1.9655</v>
       </c>
-      <c r="G16" t="n">
+      <c r="K16" t="n">
         <v>4.981</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.3145</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.8833</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.0989</v>
-      </c>
-      <c r="K16" t="n">
-        <v>5.1144</v>
       </c>
       <c r="L16" t="n">
         <v>43.29999999999998</v>
@@ -1682,22 +1682,22 @@
         <v>0.1799999999999997</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.040000000000074</v>
+        <v>-1.039999999999868</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-13</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.1334</v>
+        <v>1.1221</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1334</v>
+        <v>1.122100000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1334</v>
+        <v>1.1221</v>
       </c>
     </row>
     <row r="17">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TP.7.2</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1727,28 +1727,28 @@
         <v>5.0692</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3448</v>
+        <v>2.6481</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0292</v>
+        <v>2.3325</v>
       </c>
       <c r="J17" t="n">
-        <v>2.187</v>
+        <v>2.4903</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2025</v>
+        <v>5.5058</v>
       </c>
       <c r="L17" t="n">
         <v>31.33999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>31.56000000000003</v>
+        <v>31.55999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2200000000000415</v>
+        <v>-0.2199999999999989</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.260000000000115</v>
+        <v>-1.259999999999867</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1757,13 +1757,13 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.1332999999999998</v>
+        <v>-0.4365999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1332999999999993</v>
+        <v>-0.4365999999999994</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1332999999999995</v>
+        <v>-0.4365999999999997</v>
       </c>
     </row>
     <row r="18">
@@ -1772,25 +1772,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>K3</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>K2</t>
-        </is>
-      </c>
       <c r="D18" t="n">
-        <v>1.8757</v>
+        <v>2.0462</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6705</v>
+        <v>1.841</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7731</v>
+        <v>1.9436</v>
       </c>
       <c r="G18" t="n">
-        <v>4.7886</v>
+        <v>4.9591</v>
       </c>
       <c r="H18" t="n">
         <v>1.7792</v>
@@ -1814,22 +1814,22 @@
         <v>-0.7000000000000135</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.960000000000129</v>
+        <v>-1.95999999999988</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-13</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.09999999999999987</v>
+        <v>0.2705</v>
       </c>
       <c r="S18" t="n">
-        <v>0.09999999999999964</v>
+        <v>0.2705000000000002</v>
       </c>
       <c r="T18" t="n">
-        <v>0.09999999999999976</v>
+        <v>0.2705000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TP.9.1</t>
+          <t>TP.11.1</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1859,28 +1859,28 @@
         <v>4.6497</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0136</v>
+        <v>2.5708</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5216</v>
+        <v>2.0788</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7676</v>
+        <v>2.3248</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7831</v>
+        <v>5.3403</v>
       </c>
       <c r="L19" t="n">
         <v>49.51999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>49.19999999999997</v>
+        <v>49.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3200000000000145</v>
+        <v>0.3199999999999861</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.640000000000114</v>
+        <v>-1.639999999999894</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1889,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.1334</v>
+        <v>-0.6906000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1334</v>
+        <v>-0.6905999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1334</v>
+        <v>-0.6906</v>
       </c>
     </row>
     <row r="20">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TP.9.1</t>
+          <t>TP.11.1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TP.9.2</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1925,16 +1925,16 @@
         <v>5.1909</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4888</v>
+        <v>3.046</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1288</v>
+        <v>2.686</v>
       </c>
       <c r="J20" t="n">
-        <v>2.3088</v>
+        <v>2.866</v>
       </c>
       <c r="K20" t="n">
-        <v>5.3243</v>
+        <v>5.8815</v>
       </c>
       <c r="L20" t="n">
         <v>35.73999999999999</v>
@@ -1946,7 +1946,7 @@
         <v>-0.2599999999999909</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.900000000000105</v>
+        <v>-1.899999999999885</v>
       </c>
       <c r="P20" t="n">
         <v>-8.881784197001252e-13</v>
@@ -1955,13 +1955,13 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.1334000000000004</v>
+        <v>-0.6906000000000003</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1334</v>
+        <v>-0.6905999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1334000000000002</v>
+        <v>-0.6906000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TP.9.2</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>TP.12.1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1991,43 +1991,43 @@
         <v>4.6037</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8896</v>
+        <v>3.1049</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5534</v>
+        <v>2.7687</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7215</v>
+        <v>2.9368</v>
       </c>
       <c r="K21" t="n">
-        <v>4.737</v>
+        <v>5.9523</v>
       </c>
       <c r="L21" t="n">
         <v>33.95999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>33.62</v>
+        <v>33.62000000000003</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3399999999999892</v>
+        <v>0.3399999999999679</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.560000000000116</v>
+        <v>-1.559999999999917</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-13</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.1333</v>
+        <v>-1.3486</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1333000000000002</v>
+        <v>-1.3486</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1333000000000001</v>
+        <v>-1.3486</v>
       </c>
     </row>
     <row r="22">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>TP.12.1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>K1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>TP.10.1</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2057,28 +2057,28 @@
         <v>4.6752</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0553</v>
+        <v>3.2539</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5641</v>
+        <v>2.7627</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8097</v>
+        <v>3.0083</v>
       </c>
       <c r="K22" t="n">
-        <v>4.8252</v>
+        <v>6.0238</v>
       </c>
       <c r="L22" t="n">
         <v>49.90000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>49.11999999999998</v>
+        <v>49.11999999999996</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7800000000000296</v>
+        <v>0.7800000000000509</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7800000000000864</v>
+        <v>-0.7799999999998661</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.1500000000000001</v>
+        <v>-1.3486</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1499999999999995</v>
+        <v>-1.348599999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1499999999999998</v>
+        <v>-1.3486</v>
       </c>
     </row>
     <row r="23">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TP.10.1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2111,55 +2111,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.8145</v>
+        <v>3.84</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5233</v>
+        <v>3.5488</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6689</v>
+        <v>3.6944</v>
       </c>
       <c r="G23" t="n">
-        <v>4.6844</v>
+        <v>6.7099</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9655</v>
+        <v>1.8155</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6723</v>
+        <v>1.5223</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8201</v>
+        <v>1.6699</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8356</v>
+        <v>4.6854</v>
       </c>
       <c r="L23" t="n">
         <v>29.11999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>29.32000000000001</v>
+        <v>29.31999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2000000000000242</v>
+        <v>-0.1999999999999993</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9800000000001106</v>
+        <v>-0.9799999999998654</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-13</v>
       </c>
       <c r="Q23" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.1512</v>
+        <v>2.0245</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1512000000000002</v>
+        <v>2.024500000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1512000000000001</v>
+        <v>2.0245</v>
       </c>
     </row>
   </sheetData>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.728800 m</t>
+          <t>58.450400 m</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>46.130100 m</t>
+          <t>51.144100 m</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.598700 m</t>
+          <t>7.306300 m</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.300 mm</t>
+          <t>-1.100 mm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.910200 m</t>
+          <t>47.924500 m</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>45.511500 m</t>
+          <t>55.233000 m</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-2.601300 m</t>
+          <t>-7.308500 m</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-1.300 mm</t>
+          <t>-1.100 mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">

--- a/output/二等水准观测手簿.xlsx
+++ b/output/二等水准观测手簿.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表头" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="观测记录" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成果计算" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2363,4 +2364,651 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>点名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>距离(km)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>观测高差(m)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>改正数(mm)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>改正后高差(m)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>高程(m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TP.1.1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.09179447285265811</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.05684999999999996</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.05684999999999991</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.60675</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1835889457053162</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.05679999999999996</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.05679999999999992</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.54995</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TP.2.1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2753834185579743</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8990500000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8990500000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.449</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TP.2.2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3671778914106325</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.3603500000000002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3603500000000002</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.80935</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.4589723642632906</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2229000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2229000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.03225</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TP.3.1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.5507668371159486</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0290999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02909999999999995</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.06135</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6425613099686067</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0290999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.02909999999999995</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.09045</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.7343557828212648</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2575499999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2575499999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.348</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>K5</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.8261502556739229</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.6110999999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6110999999999998</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.959099999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9179447285265809</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.1683</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.1683</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.790799999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TP.7.1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.009739201379239</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.76315</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.76315</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.553949999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.101533674231897</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7632500000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7632500000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.317199999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TP.8.1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.193328147084555</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7631999999999998</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7631999999999998</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7.080399999999998</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.285122619937213</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7632000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7632000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.843599999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TP.9.1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.376917092789871</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.16825</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.16825</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7.675349999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TP.9.2</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.468711565642529</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6111</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6111</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8.286449999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.560506038495187</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.2575500000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2575500000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8.543999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TP.10.1</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.652300511347846</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.02915000000000012</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.02915000000000016</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8.573149999999998</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.744094984200504</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.02915000000000023</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.02915000000000027</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8.602299999999998</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.835889457053162</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4476999999999998</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.4476999999999998</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9.049999999999997</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.92768392990582</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5851500000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5851500000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9.635149999999998</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.019478402758478</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4.037174635000569e-14</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9.970999999999998</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>辅助计算项</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>闭合差(mm)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>限差(mm)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>±5.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>是否合格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>每公里改正数(mm/km)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>路线总长(km)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2.0195</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>往返测不符值(mm)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2.200</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>往返测限差(mm)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>±5.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>往返测中数高差(m)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7.30740</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/二等水准观测手簿.xlsx
+++ b/output/二等水准观测手簿.xlsx
@@ -601,12 +601,12 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -726,46 +726,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.1768</v>
+        <v>1.9707</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7278</v>
+        <v>1.5531</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9523</v>
+        <v>1.7619</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9678</v>
+        <v>4.7773</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0735</v>
+        <v>2.8694</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6293</v>
+        <v>2.4526</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8514</v>
+        <v>2.661</v>
       </c>
       <c r="K2" t="n">
-        <v>5.8669</v>
+        <v>5.6764</v>
       </c>
       <c r="L2" t="n">
-        <v>44.90000000000001</v>
+        <v>41.76</v>
       </c>
       <c r="M2" t="n">
-        <v>44.41999999999999</v>
+        <v>41.68000000000003</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4800000000000111</v>
+        <v>0.07999999999996987</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4800000000000111</v>
+        <v>0.07999999999996987</v>
       </c>
       <c r="P2" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="R2" t="n">
         <v>-0.8991</v>
@@ -792,55 +792,55 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.0664</v>
+        <v>2.3081</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7458</v>
+        <v>1.9563</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9061</v>
+        <v>2.1322</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9216</v>
+        <v>5.1477</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9653</v>
+        <v>3.2103</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6451</v>
+        <v>2.8523</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8052</v>
+        <v>3.0313</v>
       </c>
       <c r="K3" t="n">
-        <v>5.8207</v>
+        <v>6.0468</v>
       </c>
       <c r="L3" t="n">
-        <v>32.05999999999997</v>
+        <v>35.18000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>32.02000000000002</v>
+        <v>35.80000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03999999999994941</v>
+        <v>-0.6199999999999974</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5199999999999605</v>
+        <v>-0.5400000000000276</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.8991000000000002</v>
+        <v>-0.8990999999999998</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8991000000000007</v>
+        <v>-0.8990999999999998</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8991000000000005</v>
+        <v>-0.8990999999999998</v>
       </c>
     </row>
     <row r="4">
@@ -858,55 +858,55 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.3185</v>
+        <v>2.4448</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0681</v>
+        <v>2.1942</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1933</v>
+        <v>2.3195</v>
       </c>
       <c r="G4" t="n">
-        <v>5.2088</v>
+        <v>5.3351</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2146</v>
+        <v>3.3401</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9702</v>
+        <v>3.0971</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0924</v>
+        <v>3.2186</v>
       </c>
       <c r="K4" t="n">
-        <v>6.1079</v>
+        <v>6.2342</v>
       </c>
       <c r="L4" t="n">
-        <v>25.04</v>
+        <v>25.06</v>
       </c>
       <c r="M4" t="n">
-        <v>24.43999999999997</v>
+        <v>24.29999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6000000000000227</v>
+        <v>0.7600000000000051</v>
       </c>
       <c r="O4" t="n">
-        <v>1.119999999999983</v>
+        <v>0.2199999999999775</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.0001000000000006551</v>
       </c>
       <c r="R4" t="n">
+        <v>-0.8990999999999998</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.8991000000000007</v>
+      </c>
+      <c r="T4" t="n">
         <v>-0.8991000000000002</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-0.8990999999999998</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.8991</v>
       </c>
     </row>
     <row r="5">
@@ -924,55 +924,55 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.5591</v>
+        <v>2.1091</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3111</v>
+        <v>1.6467</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4351</v>
+        <v>1.8779</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4506</v>
+        <v>4.8936</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3772</v>
+        <v>1.9307</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1364</v>
+        <v>1.4685</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2568</v>
+        <v>1.6996</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2723</v>
+        <v>4.7153</v>
       </c>
       <c r="L5" t="n">
-        <v>24.79999999999998</v>
+        <v>46.24000000000002</v>
       </c>
       <c r="M5" t="n">
-        <v>24.08000000000001</v>
+        <v>46.22000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7199999999999633</v>
+        <v>0.02000000000000313</v>
       </c>
       <c r="O5" t="n">
-        <v>1.839999999999947</v>
+        <v>0.2399999999999807</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.0002000000000004221</v>
       </c>
       <c r="Q5" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>-0.0002000000000004221</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1782999999999997</v>
+        <v>0.1782999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1782999999999992</v>
+        <v>0.1783000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1782999999999995</v>
+        <v>0.1783</v>
       </c>
     </row>
     <row r="6">
@@ -990,55 +990,55 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.0556</v>
+        <v>2.667</v>
       </c>
       <c r="E6" t="n">
-        <v>2.576</v>
+        <v>2.2362</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8158</v>
+        <v>2.4516</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8313</v>
+        <v>5.4674</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6037</v>
+        <v>2.2174</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1215</v>
+        <v>1.7794</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3626</v>
+        <v>1.9984</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3781</v>
+        <v>5.0142</v>
       </c>
       <c r="L6" t="n">
-        <v>47.96</v>
+        <v>43.07999999999996</v>
       </c>
       <c r="M6" t="n">
-        <v>48.21999999999997</v>
+        <v>43.8</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2599999999999696</v>
+        <v>-0.7200000000000344</v>
       </c>
       <c r="O6" t="n">
-        <v>1.579999999999977</v>
+        <v>-0.4800000000000537</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.0002999999999993008</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.000300000000000189</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4531999999999998</v>
+        <v>0.4532</v>
       </c>
       <c r="S6" t="n">
         <v>0.4531999999999998</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4531999999999998</v>
+        <v>0.4531999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1056,55 +1056,55 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.3269</v>
+        <v>2.4103</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9977</v>
+        <v>2.0669</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1623</v>
+        <v>2.2386</v>
       </c>
       <c r="G7" t="n">
-        <v>5.1778</v>
+        <v>5.2543</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6967</v>
+        <v>1.7805</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3631</v>
+        <v>1.4321</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5299</v>
+        <v>1.6063</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5454</v>
+        <v>4.622</v>
       </c>
       <c r="L7" t="n">
-        <v>32.92000000000002</v>
+        <v>34.33999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>33.36000000000001</v>
+        <v>34.84</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4399999999999977</v>
+        <v>-0.5000000000000142</v>
       </c>
       <c r="O7" t="n">
-        <v>1.139999999999979</v>
+        <v>-0.9800000000000679</v>
       </c>
       <c r="P7" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>-0.0002000000000004221</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.0001999999999995339</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6324000000000001</v>
+        <v>0.6322999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6324000000000005</v>
+        <v>0.6322999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6324000000000003</v>
+        <v>0.6322999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1122,55 +1122,55 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.6092</v>
+        <v>2.9299</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1792</v>
+        <v>2.6931</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3942</v>
+        <v>2.8115</v>
       </c>
       <c r="G8" t="n">
-        <v>5.4097</v>
+        <v>5.8272</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9787</v>
+        <v>2.2997</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5451</v>
+        <v>2.0585</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7619</v>
+        <v>2.1791</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7774</v>
+        <v>5.1948</v>
       </c>
       <c r="L8" t="n">
-        <v>43.00000000000001</v>
+        <v>23.68000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>43.36</v>
+        <v>24.12000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3599999999999852</v>
+        <v>-0.4399999999999942</v>
       </c>
       <c r="O8" t="n">
-        <v>0.779999999999994</v>
+        <v>-1.420000000000062</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.0002000000000004221</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.0002000000000004221</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6323000000000001</v>
+        <v>0.6324000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6322999999999999</v>
+        <v>0.6324000000000005</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6323</v>
+        <v>0.6324000000000003</v>
       </c>
     </row>
     <row r="9">
@@ -1188,55 +1188,55 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.1335</v>
+        <v>2.0453</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7527</v>
+        <v>1.7319</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9431</v>
+        <v>1.8886</v>
       </c>
       <c r="G9" t="n">
-        <v>4.9586</v>
+        <v>4.9039</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9212</v>
+        <v>2.8319</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5362</v>
+        <v>2.5163</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7287</v>
+        <v>2.6741</v>
       </c>
       <c r="K9" t="n">
-        <v>5.7442</v>
+        <v>5.6894</v>
       </c>
       <c r="L9" t="n">
-        <v>38.08000000000003</v>
+        <v>31.34000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>38.49999999999998</v>
+        <v>31.55999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.419999999999952</v>
+        <v>-0.2199999999999775</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3600000000000421</v>
+        <v>-1.64000000000004</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.0001999999999995339</v>
       </c>
       <c r="Q9" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>0.0002000000000004221</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.7855999999999999</v>
+        <v>-0.7855000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7856000000000005</v>
+        <v>-0.7854999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7856000000000002</v>
+        <v>-0.7855</v>
       </c>
     </row>
     <row r="10">
@@ -1254,55 +1254,55 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.2291</v>
+        <v>1.9108</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7833</v>
+        <v>1.4354</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0062</v>
+        <v>1.6731</v>
       </c>
       <c r="G10" t="n">
-        <v>5.0217</v>
+        <v>4.6885</v>
       </c>
       <c r="H10" t="n">
-        <v>3.017</v>
+        <v>2.6935</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5666</v>
+        <v>2.2239</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7918</v>
+        <v>2.4587</v>
       </c>
       <c r="K10" t="n">
-        <v>5.8073</v>
+        <v>5.4741</v>
       </c>
       <c r="L10" t="n">
-        <v>44.57999999999998</v>
+        <v>47.54000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>45.03999999999997</v>
+        <v>46.95999999999998</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4599999999999937</v>
+        <v>0.5800000000000267</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.09999999999995168</v>
+        <v>-1.060000000000013</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.7855999999999996</v>
+        <v>-0.7855999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>-0.7855999999999996</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7855999999999996</v>
+        <v>-0.7855999999999997</v>
       </c>
     </row>
     <row r="11">
@@ -1320,55 +1320,55 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.232</v>
+        <v>1.7711</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0248</v>
+        <v>1.3685</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1284</v>
+        <v>1.5698</v>
       </c>
       <c r="G11" t="n">
-        <v>5.1439</v>
+        <v>4.5854</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0154</v>
+        <v>2.558</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8124</v>
+        <v>2.1528</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9139</v>
+        <v>2.3554</v>
       </c>
       <c r="K11" t="n">
-        <v>5.9294</v>
+        <v>5.371</v>
       </c>
       <c r="L11" t="n">
-        <v>20.72000000000003</v>
+        <v>40.25999999999998</v>
       </c>
       <c r="M11" t="n">
-        <v>20.30000000000003</v>
+        <v>40.51999999999998</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4199999999999982</v>
+        <v>-0.259999999999998</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3200000000000465</v>
+        <v>-1.320000000000011</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>-0.0001000000000006551</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.7854999999999999</v>
+        <v>-0.7855999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7854999999999999</v>
+        <v>-0.7856000000000005</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7854999999999999</v>
+        <v>-0.7856000000000002</v>
       </c>
     </row>
     <row r="12">
@@ -1386,55 +1386,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.9506</v>
+        <v>2.1331</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4882</v>
+        <v>1.9165</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7194</v>
+        <v>2.0248</v>
       </c>
       <c r="G12" t="n">
-        <v>4.7349</v>
+        <v>5.0402</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7952</v>
+        <v>2.9775</v>
       </c>
       <c r="I12" t="n">
-        <v>2.333</v>
+        <v>2.7615</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5641</v>
+        <v>2.8695</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5796</v>
+        <v>5.8849</v>
       </c>
       <c r="L12" t="n">
-        <v>46.23999999999999</v>
+        <v>21.66000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>46.21999999999997</v>
+        <v>21.60000000000002</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02000000000002444</v>
+        <v>0.05999999999999162</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3400000000000709</v>
+        <v>-1.260000000000019</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.0001000000000006551</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.8446999999999998</v>
+        <v>-0.8447</v>
       </c>
       <c r="S12" t="n">
         <v>-0.8447000000000005</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8447000000000001</v>
+        <v>-0.8447000000000002</v>
       </c>
     </row>
     <row r="13">
@@ -1452,40 +1452,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.1513</v>
+        <v>2.0409</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8455</v>
+        <v>1.5419</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9984</v>
+        <v>1.7914</v>
       </c>
       <c r="G13" t="n">
-        <v>5.0139</v>
+        <v>4.8069</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9983</v>
+        <v>2.8818</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6881</v>
+        <v>2.3906</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8432</v>
+        <v>2.6362</v>
       </c>
       <c r="K13" t="n">
-        <v>5.8587</v>
+        <v>5.6517</v>
       </c>
       <c r="L13" t="n">
-        <v>30.58000000000001</v>
+        <v>49.90000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>31.02</v>
+        <v>49.12</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4399999999999977</v>
+        <v>0.7800000000000082</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.09999999999992681</v>
+        <v>-0.4800000000000111</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1518,55 +1518,55 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.6314</v>
+        <v>1.8616</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2786</v>
+        <v>1.4762</v>
       </c>
       <c r="F14" t="n">
-        <v>2.455</v>
+        <v>1.6689</v>
       </c>
       <c r="G14" t="n">
-        <v>5.4705</v>
+        <v>4.6845</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3161</v>
+        <v>2.5398</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9573</v>
+        <v>2.1612</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1367</v>
+        <v>2.3505</v>
       </c>
       <c r="K14" t="n">
-        <v>6.1522</v>
+        <v>5.3661</v>
       </c>
       <c r="L14" t="n">
-        <v>35.28000000000002</v>
+        <v>38.54</v>
       </c>
       <c r="M14" t="n">
-        <v>35.88</v>
+        <v>37.86000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5999999999999801</v>
+        <v>0.6799999999999926</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6999999999999069</v>
+        <v>0.1999999999999815</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.0001000000000006551</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.6816999999999998</v>
+        <v>-0.6815999999999998</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6816999999999993</v>
+        <v>-0.6816000000000004</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6816999999999995</v>
+        <v>-0.6816000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1584,40 +1584,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.18</v>
+        <v>2.0555</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7762</v>
+        <v>1.6841</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9781</v>
+        <v>1.8698</v>
       </c>
       <c r="G15" t="n">
-        <v>4.9936</v>
+        <v>4.8853</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8642</v>
+        <v>2.7388</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4552</v>
+        <v>2.364</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6597</v>
+        <v>2.5514</v>
       </c>
       <c r="K15" t="n">
-        <v>5.6752</v>
+        <v>5.5669</v>
       </c>
       <c r="L15" t="n">
-        <v>40.38000000000002</v>
+        <v>37.13999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>40.89999999999998</v>
+        <v>37.48</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5199999999999605</v>
+        <v>-0.3400000000000105</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.219999999999867</v>
+        <v>-0.140000000000029</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1626,13 +1626,13 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.6816</v>
+        <v>-0.6816000000000002</v>
       </c>
       <c r="S15" t="n">
         <v>-0.6816000000000004</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6816000000000002</v>
+        <v>-0.6816000000000003</v>
       </c>
     </row>
     <row r="16">
@@ -1650,43 +1650,43 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.3041</v>
+        <v>3.5167</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8711</v>
+        <v>3.2929</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0876</v>
+        <v>3.4048</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1031</v>
+        <v>6.4203</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1811</v>
+        <v>2.3929</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7499</v>
+        <v>2.1725</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9655</v>
+        <v>2.2827</v>
       </c>
       <c r="K16" t="n">
-        <v>4.981</v>
+        <v>5.2982</v>
       </c>
       <c r="L16" t="n">
-        <v>43.29999999999998</v>
+        <v>22.38000000000002</v>
       </c>
       <c r="M16" t="n">
-        <v>43.11999999999998</v>
+        <v>22.04000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1799999999999997</v>
+        <v>0.3400000000000105</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.039999999999868</v>
+        <v>0.1999999999999815</v>
       </c>
       <c r="P16" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1716,55 +1716,55 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.2104</v>
+        <v>2.7007</v>
       </c>
       <c r="E17" t="n">
-        <v>1.897</v>
+        <v>2.2895</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0537</v>
+        <v>2.4951</v>
       </c>
       <c r="G17" t="n">
-        <v>5.0692</v>
+        <v>5.5107</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6481</v>
+        <v>3.141</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3325</v>
+        <v>2.7224</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4903</v>
+        <v>2.9317</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5058</v>
+        <v>5.9473</v>
       </c>
       <c r="L17" t="n">
-        <v>31.33999999999999</v>
+        <v>41.12</v>
       </c>
       <c r="M17" t="n">
-        <v>31.55999999999999</v>
+        <v>41.86000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2199999999999989</v>
+        <v>-0.740000000000002</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.259999999999867</v>
+        <v>-0.5400000000000205</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.4365999999999999</v>
+        <v>-0.4366000000000003</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4365999999999994</v>
+        <v>-0.4366000000000003</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4365999999999997</v>
+        <v>-0.4366000000000003</v>
       </c>
     </row>
     <row r="18">
@@ -1782,55 +1782,55 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.0462</v>
+        <v>2.6005</v>
       </c>
       <c r="E18" t="n">
-        <v>1.841</v>
+        <v>2.1787</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9436</v>
+        <v>2.3896</v>
       </c>
       <c r="G18" t="n">
-        <v>4.9591</v>
+        <v>5.4051</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7792</v>
+        <v>2.3337</v>
       </c>
       <c r="I18" t="n">
-        <v>1.567</v>
+        <v>1.9045</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6731</v>
+        <v>2.1191</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6886</v>
+        <v>5.1346</v>
       </c>
       <c r="L18" t="n">
-        <v>20.51999999999998</v>
+        <v>42.17999999999997</v>
       </c>
       <c r="M18" t="n">
-        <v>21.22</v>
+        <v>42.91999999999998</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7000000000000135</v>
+        <v>-0.7400000000000091</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.95999999999988</v>
+        <v>-1.28000000000003</v>
       </c>
       <c r="P18" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2705</v>
+        <v>0.2705000000000002</v>
       </c>
       <c r="S18" t="n">
         <v>0.2705000000000002</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2705000000000001</v>
+        <v>0.2705000000000002</v>
       </c>
     </row>
     <row r="19">
@@ -1848,55 +1848,55 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.8818</v>
+        <v>2.3135</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3866</v>
+        <v>1.9321</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6342</v>
+        <v>2.1228</v>
       </c>
       <c r="G19" t="n">
-        <v>4.6497</v>
+        <v>5.1383</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5708</v>
+        <v>3.0015</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0788</v>
+        <v>2.6253</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3248</v>
+        <v>2.8134</v>
       </c>
       <c r="K19" t="n">
-        <v>5.3403</v>
+        <v>5.8289</v>
       </c>
       <c r="L19" t="n">
-        <v>49.51999999999999</v>
+        <v>38.13999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>49.2</v>
+        <v>37.61999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3199999999999861</v>
+        <v>0.5200000000000031</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.639999999999894</v>
+        <v>-0.7600000000000264</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.6906000000000001</v>
+        <v>-0.6906000000000003</v>
       </c>
       <c r="S19" t="n">
         <v>-0.6905999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6906</v>
+        <v>-0.6906000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1914,55 +1914,55 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.3541</v>
+        <v>2.2743</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9967</v>
+        <v>1.7837</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1754</v>
+        <v>2.029</v>
       </c>
       <c r="G20" t="n">
-        <v>5.1909</v>
+        <v>5.0443</v>
       </c>
       <c r="H20" t="n">
-        <v>3.046</v>
+        <v>2.967</v>
       </c>
       <c r="I20" t="n">
-        <v>2.686</v>
+        <v>2.4722</v>
       </c>
       <c r="J20" t="n">
-        <v>2.866</v>
+        <v>2.7196</v>
       </c>
       <c r="K20" t="n">
-        <v>5.8815</v>
+        <v>5.7349</v>
       </c>
       <c r="L20" t="n">
-        <v>35.73999999999999</v>
+        <v>49.06000000000002</v>
       </c>
       <c r="M20" t="n">
-        <v>35.99999999999999</v>
+        <v>49.48000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2599999999999909</v>
+        <v>-0.4199999999999946</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.899999999999885</v>
+        <v>-1.180000000000021</v>
       </c>
       <c r="P20" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>0.0001999999999995339</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>0.0001999999999995339</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.6906000000000003</v>
+        <v>-0.6905999999999999</v>
       </c>
       <c r="S20" t="n">
         <v>-0.6905999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6906000000000001</v>
+        <v>-0.6905999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1980,46 +1980,46 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.758</v>
+        <v>2.1862</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4184</v>
+        <v>1.9654</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5882</v>
+        <v>2.0758</v>
       </c>
       <c r="G21" t="n">
-        <v>4.6037</v>
+        <v>5.0912</v>
       </c>
       <c r="H21" t="n">
-        <v>3.1049</v>
+        <v>3.5362</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7687</v>
+        <v>3.3126</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9368</v>
+        <v>3.4244</v>
       </c>
       <c r="K21" t="n">
-        <v>5.9523</v>
+        <v>6.4398</v>
       </c>
       <c r="L21" t="n">
-        <v>33.95999999999999</v>
+        <v>22.07999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>33.62000000000003</v>
+        <v>22.35999999999998</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3399999999999679</v>
+        <v>-0.2799999999999905</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.559999999999917</v>
+        <v>-1.460000000000012</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.0001000000000006551</v>
       </c>
       <c r="Q21" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="R21" t="n">
         <v>-1.3486</v>
@@ -2046,52 +2046,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.9092</v>
+        <v>2.5034</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4102</v>
+        <v>2.148</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6597</v>
+        <v>2.3257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.6752</v>
+        <v>5.3414</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2539</v>
+        <v>3.8526</v>
       </c>
       <c r="I22" t="n">
-        <v>2.7627</v>
+        <v>3.496</v>
       </c>
       <c r="J22" t="n">
-        <v>3.0083</v>
+        <v>3.6743</v>
       </c>
       <c r="K22" t="n">
-        <v>6.0238</v>
+        <v>6.69</v>
       </c>
       <c r="L22" t="n">
-        <v>49.90000000000001</v>
+        <v>35.53999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>49.11999999999996</v>
+        <v>35.65999999999998</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7800000000000509</v>
+        <v>-0.1199999999999903</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7799999999998661</v>
+        <v>-1.580000000000002</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.0002000000000004221</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.0002000000000004221</v>
       </c>
       <c r="R22" t="n">
         <v>-1.3486</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.348599999999999</v>
+        <v>-1.3486</v>
       </c>
       <c r="T22" t="n">
         <v>-1.3486</v>
@@ -2112,55 +2112,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3.84</v>
+        <v>4.6034</v>
       </c>
       <c r="E23" t="n">
-        <v>3.5488</v>
+        <v>4.1902</v>
       </c>
       <c r="F23" t="n">
-        <v>3.6944</v>
+        <v>4.3968</v>
       </c>
       <c r="G23" t="n">
-        <v>6.7099</v>
+        <v>7.4121</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8155</v>
+        <v>2.5769</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5223</v>
+        <v>2.1657</v>
       </c>
       <c r="J23" t="n">
-        <v>1.6699</v>
+        <v>2.3704</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6854</v>
+        <v>5.3857</v>
       </c>
       <c r="L23" t="n">
-        <v>29.11999999999999</v>
+        <v>41.31999999999998</v>
       </c>
       <c r="M23" t="n">
-        <v>29.31999999999999</v>
+        <v>41.12</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1999999999999993</v>
+        <v>0.1999999999999744</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9799999999998654</v>
+        <v>-1.380000000000027</v>
       </c>
       <c r="P23" t="n">
-        <v>-8.881784197001252e-13</v>
+        <v>0.0002000000000004221</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>0.0001999999999995339</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0245</v>
+        <v>2.0264</v>
       </c>
       <c r="S23" t="n">
-        <v>2.024500000000001</v>
+        <v>2.0264</v>
       </c>
       <c r="T23" t="n">
-        <v>2.0245</v>
+        <v>2.0264</v>
       </c>
     </row>
   </sheetData>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.450400 m</t>
+          <t>54.124200 m</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>51.144100 m</t>
+          <t>46.815400 m</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.306300 m</t>
+          <t>7.308800 m</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.816 km</t>
+          <t>0.794 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.100 mm</t>
+          <t>1.400 mm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.924500 m</t>
+          <t>49.319200 m</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>55.233000 m</t>
+          <t>56.625700 m</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-7.308500 m</t>
+          <t>-7.306500 m</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.800 km</t>
+          <t>0.808 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-1.100 mm</t>
+          <t>0.900 mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2428,13 +2428,13 @@
         <v>-0.05684999999999996</v>
       </c>
       <c r="D2" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.05684999999999991</v>
+        <v>-0.05686136363636361</v>
       </c>
       <c r="F2" t="n">
-        <v>2.60675</v>
+        <v>2.606738636363636</v>
       </c>
     </row>
     <row r="3">
@@ -2447,16 +2447,16 @@
         <v>0.1835889457053162</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05679999999999996</v>
+        <v>-0.05685000000000018</v>
       </c>
       <c r="D3" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.05679999999999992</v>
+        <v>-0.05686136363636383</v>
       </c>
       <c r="F3" t="n">
-        <v>2.54995</v>
+        <v>2.549877272727272</v>
       </c>
     </row>
     <row r="4">
@@ -2469,16 +2469,16 @@
         <v>0.2753834185579743</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8990500000000001</v>
+        <v>0.8991</v>
       </c>
       <c r="D4" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8990500000000001</v>
+        <v>0.8990886363636363</v>
       </c>
       <c r="F4" t="n">
-        <v>3.449</v>
+        <v>3.448965909090909</v>
       </c>
     </row>
     <row r="5">
@@ -2491,16 +2491,16 @@
         <v>0.3671778914106325</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3603500000000002</v>
+        <v>0.3604000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3603500000000002</v>
+        <v>0.3603886363636364</v>
       </c>
       <c r="F5" t="n">
-        <v>3.80935</v>
+        <v>3.809354545454545</v>
       </c>
     </row>
     <row r="6">
@@ -2513,16 +2513,16 @@
         <v>0.4589723642632906</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2229000000000001</v>
+        <v>0.2229499999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2229000000000001</v>
+        <v>0.2229386363636362</v>
       </c>
       <c r="F6" t="n">
-        <v>4.03225</v>
+        <v>4.032293181818181</v>
       </c>
     </row>
     <row r="7">
@@ -2535,16 +2535,16 @@
         <v>0.5507668371159486</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0290999999999999</v>
+        <v>0.02910000000000013</v>
       </c>
       <c r="D7" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02909999999999995</v>
+        <v>0.02908863636363648</v>
       </c>
       <c r="F7" t="n">
-        <v>4.06135</v>
+        <v>4.061381818181817</v>
       </c>
     </row>
     <row r="8">
@@ -2557,16 +2557,16 @@
         <v>0.6425613099686067</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0290999999999999</v>
+        <v>0.02905000000000002</v>
       </c>
       <c r="D8" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02909999999999995</v>
+        <v>0.02903863636363637</v>
       </c>
       <c r="F8" t="n">
-        <v>4.09045</v>
+        <v>4.090420454545454</v>
       </c>
     </row>
     <row r="9">
@@ -2579,16 +2579,16 @@
         <v>0.7343557828212648</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2575499999999998</v>
+        <v>0.2575000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2575499999999999</v>
+        <v>0.2574886363636364</v>
       </c>
       <c r="F9" t="n">
-        <v>4.348</v>
+        <v>4.34790909090909</v>
       </c>
     </row>
     <row r="10">
@@ -2601,16 +2601,16 @@
         <v>0.8261502556739229</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6110999999999998</v>
+        <v>0.6111</v>
       </c>
       <c r="D10" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6110999999999998</v>
+        <v>0.6110886363636363</v>
       </c>
       <c r="F10" t="n">
-        <v>4.959099999999999</v>
+        <v>4.958997727272726</v>
       </c>
     </row>
     <row r="11">
@@ -2623,16 +2623,16 @@
         <v>0.9179447285265809</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1683</v>
+        <v>-0.1682499999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1683</v>
+        <v>-0.1682613636363635</v>
       </c>
       <c r="F11" t="n">
-        <v>4.790799999999999</v>
+        <v>4.790736363636362</v>
       </c>
     </row>
     <row r="12">
@@ -2645,16 +2645,16 @@
         <v>1.009739201379239</v>
       </c>
       <c r="C12" t="n">
-        <v>0.76315</v>
+        <v>0.7631999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E12" t="n">
-        <v>0.76315</v>
+        <v>0.7631886363636362</v>
       </c>
       <c r="F12" t="n">
-        <v>5.553949999999999</v>
+        <v>5.553924999999998</v>
       </c>
     </row>
     <row r="13">
@@ -2667,16 +2667,16 @@
         <v>1.101533674231897</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7632500000000001</v>
+        <v>0.7632</v>
       </c>
       <c r="D13" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7632500000000001</v>
+        <v>0.7631886363636363</v>
       </c>
       <c r="F13" t="n">
-        <v>6.317199999999999</v>
+        <v>6.317113636363634</v>
       </c>
     </row>
     <row r="14">
@@ -2689,16 +2689,16 @@
         <v>1.193328147084555</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7631999999999998</v>
+        <v>0.7632</v>
       </c>
       <c r="D14" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7631999999999998</v>
+        <v>0.7631886363636363</v>
       </c>
       <c r="F14" t="n">
-        <v>7.080399999999998</v>
+        <v>7.08030227272727</v>
       </c>
     </row>
     <row r="15">
@@ -2711,16 +2711,16 @@
         <v>1.285122619937213</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7632000000000001</v>
+        <v>0.7631500000000002</v>
       </c>
       <c r="D15" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7632000000000001</v>
+        <v>0.7631386363636365</v>
       </c>
       <c r="F15" t="n">
-        <v>7.843599999999999</v>
+        <v>7.843440909090907</v>
       </c>
     </row>
     <row r="16">
@@ -2733,16 +2733,16 @@
         <v>1.376917092789871</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.16825</v>
+        <v>-0.1682499999999998</v>
       </c>
       <c r="D16" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.16825</v>
+        <v>-0.1682613636363634</v>
       </c>
       <c r="F16" t="n">
-        <v>7.675349999999999</v>
+        <v>7.675179545454544</v>
       </c>
     </row>
     <row r="17">
@@ -2755,16 +2755,16 @@
         <v>1.468711565642529</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6111</v>
+        <v>0.6111000000000002</v>
       </c>
       <c r="D17" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6111</v>
+        <v>0.6110886363636365</v>
       </c>
       <c r="F17" t="n">
-        <v>8.286449999999999</v>
+        <v>8.28626818181818</v>
       </c>
     </row>
     <row r="18">
@@ -2777,16 +2777,16 @@
         <v>1.560506038495187</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2575500000000001</v>
+        <v>0.2574999999999998</v>
       </c>
       <c r="D18" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2575500000000001</v>
+        <v>0.2574886363636362</v>
       </c>
       <c r="F18" t="n">
-        <v>8.543999999999999</v>
+        <v>8.543756818181816</v>
       </c>
     </row>
     <row r="19">
@@ -2799,16 +2799,16 @@
         <v>1.652300511347846</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02915000000000012</v>
+        <v>0.02915000000000023</v>
       </c>
       <c r="D19" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02915000000000016</v>
+        <v>0.02913863636363658</v>
       </c>
       <c r="F19" t="n">
-        <v>8.573149999999998</v>
+        <v>8.572895454545453</v>
       </c>
     </row>
     <row r="20">
@@ -2821,16 +2821,16 @@
         <v>1.744094984200504</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02915000000000023</v>
+        <v>0.02910000000000013</v>
       </c>
       <c r="D20" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02915000000000027</v>
+        <v>0.02908863636363648</v>
       </c>
       <c r="F20" t="n">
-        <v>8.602299999999998</v>
+        <v>8.60198409090909</v>
       </c>
     </row>
     <row r="21">
@@ -2846,13 +2846,13 @@
         <v>0.4476999999999998</v>
       </c>
       <c r="D21" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4476999999999998</v>
+        <v>0.4476886363636361</v>
       </c>
       <c r="F21" t="n">
-        <v>9.049999999999997</v>
+        <v>9.049672727272727</v>
       </c>
     </row>
     <row r="22">
@@ -2865,16 +2865,16 @@
         <v>1.92768392990582</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5851500000000001</v>
+        <v>0.5851500000000002</v>
       </c>
       <c r="D22" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5851500000000001</v>
+        <v>0.5851386363636365</v>
       </c>
       <c r="F22" t="n">
-        <v>9.635149999999998</v>
+        <v>9.634811363636363</v>
       </c>
     </row>
     <row r="23">
@@ -2887,13 +2887,13 @@
         <v>2.019478402758478</v>
       </c>
       <c r="C23" t="n">
-        <v>0.33585</v>
+        <v>0.3361999999999998</v>
       </c>
       <c r="D23" t="n">
-        <v>4.037174635000569e-14</v>
+        <v>-0.01136363636365025</v>
       </c>
       <c r="E23" t="n">
-        <v>0.33585</v>
+        <v>0.3361886363636362</v>
       </c>
       <c r="F23" t="n">
         <v>9.970999999999998</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.250</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>-0.124</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>2.300</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7.30740</t>
+          <t>7.30765</t>
         </is>
       </c>
     </row>
